--- a/accountant-skill/data/output/Oct2025/trial_balance_Oct2025.xlsx
+++ b/accountant-skill/data/output/Oct2025/trial_balance_Oct2025.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dr: 1,780,718,170.12 | Cr: 1,781,931,869.05</t>
+          <t>Dr: 2,237,543,394.10 | Cr: 2,238,757,093.03</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dr: 2,290,847,209.32 | Cr: 2,292,060,908.25</t>
+          <t>Dr: 2,753,448,639.99 | Cr: 2,754,662,338.92</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>910654.5</v>
+        <v>6515831.500000004</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>8507511.76</v>
@@ -658,7 +658,7 @@
         <v>6515831.8</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2902334.46</v>
+        <v>8507511.460000005</v>
       </c>
     </row>
     <row r="9">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7444318.599999998</v>
+        <v>15343618.6</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>8810565.51</v>
@@ -680,7 +680,7 @@
         <v>15343618</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>911266.1099999975</v>
+        <v>8810566.109999999</v>
       </c>
     </row>
     <row r="10">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>16740899.02</v>
+        <v>17720746.98</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>23496953.69</v>
@@ -702,7 +702,7 @@
         <v>17720747</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10964692.33</v>
+        <v>23496953.67</v>
       </c>
     </row>
     <row r="11">
@@ -783,12 +783,12 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>210290000</v>
+        <v>429290000</v>
       </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n">
-        <v>210290000</v>
+        <v>429290000</v>
       </c>
     </row>
     <row r="16">
@@ -801,12 +801,12 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>316445000</v>
+        <v>449445000</v>
       </c>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n">
-        <v>316445000</v>
+        <v>449445000</v>
       </c>
     </row>
     <row r="17">
@@ -819,14 +819,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4433334.68</v>
+        <v>24383334.68000001</v>
       </c>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n">
         <v>554167</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4987501.68</v>
+        <v>24937501.68000001</v>
       </c>
     </row>
     <row r="18">
@@ -839,14 +839,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>71574300</v>
+        <v>137974300</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>128000</v>
       </c>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n">
-        <v>71702300</v>
+        <v>138102300</v>
       </c>
     </row>
     <row r="19">
@@ -859,14 +859,14 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>10794635.33</v>
+        <v>23169935.33</v>
       </c>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n">
         <v>1491669</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>12286304.33</v>
+        <v>24661604.33</v>
       </c>
     </row>
     <row r="20">
@@ -907,12 +907,12 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>98881000</v>
+        <v>106081000</v>
       </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n">
-        <v>98881000</v>
+        <v>106081000</v>
       </c>
     </row>
     <row r="23">
@@ -925,14 +925,14 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2396484.33</v>
+        <v>4106484.33</v>
       </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n">
         <v>331650</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2728134.33</v>
+        <v>4438134.33</v>
       </c>
     </row>
     <row r="24">
@@ -1077,14 +1077,14 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1000000000</v>
+        <v>1439530823</v>
       </c>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n">
         <v>450000000</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1450000000</v>
+        <v>1889530823</v>
       </c>
     </row>
     <row r="34">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B65" s="6" t="n"/>
       <c r="C65" s="7" t="n">
-        <v>1781931869.05</v>
+        <v>2238757093.03</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>817611890.6899999</v>
@@ -1650,7 +1650,7 @@
         <v>817611890.6899999</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>2292060908.25</v>
+        <v>2754662338.92</v>
       </c>
     </row>
   </sheetData>
